--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_11-02-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_11-02-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="230">
   <si>
     <t>SKU</t>
   </si>
@@ -577,6 +577,45 @@
     <t>£727.5</t>
   </si>
   <si>
+    <t>£10.48</t>
+  </si>
+  <si>
+    <t>£12.15</t>
+  </si>
+  <si>
+    <t>£19.75</t>
+  </si>
+  <si>
+    <t>£25.47</t>
+  </si>
+  <si>
+    <t>£33.99</t>
+  </si>
+  <si>
+    <t>£33.38</t>
+  </si>
+  <si>
+    <t>£40.99</t>
+  </si>
+  <si>
+    <t>£42.35</t>
+  </si>
+  <si>
+    <t>£103.22</t>
+  </si>
+  <si>
+    <t>£89.41</t>
+  </si>
+  <si>
+    <t>£518.2</t>
+  </si>
+  <si>
+    <t>£513.3</t>
+  </si>
+  <si>
+    <t>£488.4</t>
+  </si>
+  <si>
     <t>£12.19</t>
   </si>
   <si>
@@ -602,9 +641,6 @@
   </si>
   <si>
     <t>£26.74</t>
-  </si>
-  <si>
-    <t>£32.42</t>
   </si>
   <si>
     <t>£33.04</t>
@@ -1128,7 +1164,7 @@
         <v>89</v>
       </c>
       <c r="O2" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="P2" t="s">
         <v>89</v>
@@ -1137,7 +1173,7 @@
         <v>66</v>
       </c>
       <c r="R2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1184,16 +1220,16 @@
         <v>89</v>
       </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>188</v>
       </c>
       <c r="P3" t="s">
         <v>89</v>
       </c>
       <c r="Q3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="R3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1240,16 +1276,16 @@
         <v>89</v>
       </c>
       <c r="O4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="P4" t="s">
         <v>89</v>
       </c>
       <c r="Q4" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="R4" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1296,16 +1332,16 @@
         <v>89</v>
       </c>
       <c r="O5" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="P5" t="s">
         <v>89</v>
       </c>
       <c r="Q5" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="R5" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1352,16 +1388,16 @@
         <v>89</v>
       </c>
       <c r="O6" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="P6" t="s">
         <v>89</v>
       </c>
       <c r="Q6" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="R6" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1408,16 +1444,16 @@
         <v>89</v>
       </c>
       <c r="O7" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="P7" t="s">
         <v>89</v>
       </c>
       <c r="Q7" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="R7" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1464,16 +1500,16 @@
         <v>89</v>
       </c>
       <c r="O8" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
         <v>89</v>
       </c>
       <c r="Q8" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="R8" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1520,16 +1556,16 @@
         <v>89</v>
       </c>
       <c r="O9" t="s">
-        <v>89</v>
+        <v>190</v>
       </c>
       <c r="P9" t="s">
         <v>89</v>
       </c>
       <c r="Q9" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="R9" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1576,16 +1612,16 @@
         <v>89</v>
       </c>
       <c r="O10" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="P10" t="s">
         <v>89</v>
       </c>
       <c r="Q10" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="R10" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1632,16 +1668,16 @@
         <v>89</v>
       </c>
       <c r="O11" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="P11" t="s">
         <v>89</v>
       </c>
       <c r="Q11" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="R11" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1688,13 +1724,13 @@
         <v>89</v>
       </c>
       <c r="O12" t="s">
-        <v>89</v>
+        <v>191</v>
       </c>
       <c r="P12" t="s">
         <v>89</v>
       </c>
       <c r="Q12" t="s">
-        <v>196</v>
+        <v>89</v>
       </c>
       <c r="R12" t="s">
         <v>90</v>
@@ -1744,16 +1780,16 @@
         <v>89</v>
       </c>
       <c r="O13" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="P13" t="s">
         <v>89</v>
       </c>
       <c r="Q13" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="R13" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1800,13 +1836,13 @@
         <v>89</v>
       </c>
       <c r="O14" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="P14" t="s">
         <v>89</v>
       </c>
       <c r="Q14" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="R14" t="s">
         <v>90</v>
@@ -1856,13 +1892,13 @@
         <v>89</v>
       </c>
       <c r="O15" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="P15" t="s">
         <v>89</v>
       </c>
       <c r="Q15" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="R15" t="s">
         <v>90</v>
@@ -1912,16 +1948,16 @@
         <v>89</v>
       </c>
       <c r="O16" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="P16" t="s">
         <v>89</v>
       </c>
       <c r="Q16" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="R16" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2024,7 +2060,7 @@
         <v>89</v>
       </c>
       <c r="O18" t="s">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="P18" t="s">
         <v>89</v>
@@ -2033,7 +2069,7 @@
         <v>90</v>
       </c>
       <c r="R18" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2080,7 +2116,7 @@
         <v>89</v>
       </c>
       <c r="O19" t="s">
-        <v>89</v>
+        <v>196</v>
       </c>
       <c r="P19" t="s">
         <v>89</v>
@@ -2089,7 +2125,7 @@
         <v>90</v>
       </c>
       <c r="R19" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2304,7 +2340,7 @@
         <v>89</v>
       </c>
       <c r="O23" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="P23" t="s">
         <v>90</v>
@@ -2313,7 +2349,7 @@
         <v>90</v>
       </c>
       <c r="R23" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2360,7 +2396,7 @@
         <v>89</v>
       </c>
       <c r="O24" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="P24" t="s">
         <v>90</v>
@@ -2369,7 +2405,7 @@
         <v>90</v>
       </c>
       <c r="R24" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2416,7 +2452,7 @@
         <v>89</v>
       </c>
       <c r="O25" t="s">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="P25" t="s">
         <v>90</v>
@@ -2425,7 +2461,7 @@
         <v>90</v>
       </c>
       <c r="R25" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
